--- a/作業票.xlsx
+++ b/作業票.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\3DRPG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coop2\Project-Chi2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80ABC1F3-3189-4FED-8F49-600E0B78824F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B54DBA-C0A8-4EA4-B677-2DAF88BD687F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{41B48087-E4EE-4E9E-AF83-941FF13AEAD0}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="25">
   <si>
     <t>タスク</t>
     <phoneticPr fontId="1"/>
@@ -239,6 +239,10 @@
     <rPh sb="19" eb="22">
       <t>ヨウソウダン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラクターチェンジ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -487,7 +491,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -533,10 +537,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
@@ -931,7 +932,7 @@
       <c r="C2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -1011,10 +1012,14 @@
       <c r="B7" s="8">
         <v>5</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3"/>
+      <c r="C7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F7" s="10"/>
     </row>
@@ -1271,12 +1276,12 @@
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.7">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>21</v>
       </c>
     </row>

--- a/作業票.xlsx
+++ b/作業票.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\3DRPG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\Project-Chi2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80ABC1F3-3189-4FED-8F49-600E0B78824F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B298382-A1C8-4073-8531-F88D69CB41DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{41B48087-E4EE-4E9E-AF83-941FF13AEAD0}"/>
   </bookViews>
@@ -487,7 +487,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -533,10 +533,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
@@ -931,7 +928,7 @@
       <c r="C2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>22</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -1271,12 +1268,12 @@
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.7">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>21</v>
       </c>
     </row>

--- a/作業票.xlsx
+++ b/作業票.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\Project-Chi2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B298382-A1C8-4073-8531-F88D69CB41DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B166ED2-690A-49AE-9A06-3CA19C2E2A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{41B48087-E4EE-4E9E-AF83-941FF13AEAD0}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
   <si>
     <t>タスク</t>
     <phoneticPr fontId="1"/>
@@ -238,6 +238,114 @@
     </rPh>
     <rPh sb="19" eb="22">
       <t>ヨウソウダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インベントリ作成</t>
+    <rPh sb="6" eb="8">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細は以下の通り</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>くめた</t>
+  </si>
+  <si>
+    <t>インベントリ１：アイテム入手</t>
+    <rPh sb="12" eb="14">
+      <t>ニュウシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インベントリ２：アイテム消費</t>
+    <rPh sb="12" eb="14">
+      <t>ショウヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インベントリ３：指定アイテム数確認</t>
+    <rPh sb="8" eb="10">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インベントリ４：所持アイテム表示</t>
+    <rPh sb="8" eb="10">
+      <t>ショジ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕様書はまだ。</t>
+    <rPh sb="0" eb="3">
+      <t>シヨウショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フロー作成中</t>
+    <rPh sb="3" eb="6">
+      <t>サクセイチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>岩渕君とざっくりと仕様を確認してから？</t>
+    <rPh sb="0" eb="3">
+      <t>イワブチクン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムインターフェース</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SP回復</t>
+    <rPh sb="2" eb="4">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラ切り替え</t>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -246,7 +354,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,12 +369,6 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -487,7 +589,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -516,9 +618,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
@@ -928,7 +1027,7 @@
       <c r="C2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="15" t="s">
         <v>22</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -951,7 +1050,7 @@
       <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1008,65 +1107,99 @@
       <c r="B7" s="8">
         <v>5</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3"/>
+      <c r="C7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="10"/>
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B8" s="8">
         <v>6</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="3"/>
+      <c r="C8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="E8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B9" s="8">
         <v>7</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="3"/>
+      <c r="C9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="E9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B10" s="8">
         <v>8</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="3"/>
+      <c r="C10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="E10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B11" s="8">
         <v>9</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="3"/>
+      <c r="C11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="E11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B12" s="8">
         <v>10</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="3"/>
+      <c r="C12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="E12" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -1074,7 +1207,9 @@
       <c r="B13" s="8">
         <v>11</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="D13" s="3"/>
       <c r="E13" s="1" t="s">
         <v>3</v>
@@ -1085,7 +1220,9 @@
       <c r="B14" s="8">
         <v>12</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="D14" s="3"/>
       <c r="E14" s="1" t="s">
         <v>3</v>
@@ -1252,18 +1389,18 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.7">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1273,7 +1410,7 @@
       </c>
     </row>
     <row r="6" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>21</v>
       </c>
     </row>

--- a/作業票.xlsx
+++ b/作業票.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\Project-Chi2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B166ED2-690A-49AE-9A06-3CA19C2E2A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63385BF2-2FE6-4A25-991F-AF3152747FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{41B48087-E4EE-4E9E-AF83-941FF13AEAD0}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="36">
   <si>
     <t>タスク</t>
     <phoneticPr fontId="1"/>
@@ -78,44 +78,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Stater Assetという外部アセットを使用。けんご君の操作確認をくめたが確認し、運用可能と判断。
-なおコードは全く分からない。</t>
-    <rPh sb="15" eb="17">
-      <t>ガイブ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>クン</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ウンヨウ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>カノウ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ハンダン</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>マッタ</t>
-    </rPh>
-    <rPh sb="60" eb="61">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>弱攻撃</t>
     <rPh sb="0" eb="3">
       <t>ジャクコウゲキ</t>
@@ -130,31 +92,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">ダメージ判定は未実装。範囲：半径1m, 角度-30~30度前方　 </t>
-    <rPh sb="4" eb="6">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>ミジッソウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ハンイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ハンケイ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>カクド</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ゼンポウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ダメージ計算</t>
     <rPh sb="4" eb="6">
       <t>ケイサン</t>
@@ -223,25 +160,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>運、相性倍率（表示問題）のデータ形式は要相談。</t>
-    <rPh sb="0" eb="1">
-      <t>ウン</t>
-    </rPh>
-    <rPh sb="2" eb="6">
-      <t>アイショウバイリツ</t>
-    </rPh>
-    <rPh sb="7" eb="11">
-      <t>ヒョウジモンダイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ケイシキ</t>
-    </rPh>
-    <rPh sb="19" eb="22">
-      <t>ヨウソウダン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>インベントリ作成</t>
     <rPh sb="6" eb="8">
       <t>サクセイ</t>
@@ -346,6 +264,47 @@
     </rPh>
     <rPh sb="5" eb="6">
       <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stater Assetという外部アセットを使用。けんご君の操作確認をくめたが確認し、運用可能と判断。</t>
+    <rPh sb="15" eb="17">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>クン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ウンヨウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ハンダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>運は削除</t>
+    <rPh sb="0" eb="1">
+      <t>ウン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1028,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>1</v>
@@ -1037,7 +996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="52.9" x14ac:dyDescent="0.7">
+    <row r="3" spans="2:6" ht="35.25" x14ac:dyDescent="0.7">
       <c r="B3" s="8">
         <v>1</v>
       </c>
@@ -1045,13 +1004,13 @@
         <v>5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.7">
@@ -1059,30 +1018,28 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B5" s="8">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -1091,16 +1048,16 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.7">
@@ -1108,16 +1065,16 @@
         <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.7">
@@ -1125,16 +1082,16 @@
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.7">
@@ -1142,16 +1099,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.7">
@@ -1159,16 +1116,16 @@
         <v>8</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.7">
@@ -1176,16 +1133,16 @@
         <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.7">
@@ -1193,13 +1150,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -1208,7 +1165,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="1" t="s">
@@ -1221,7 +1178,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="1" t="s">
@@ -1374,15 +1331,15 @@
   <sheetData>
     <row r="1" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.75">
       <c r="B1" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.7">
       <c r="B2" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>3</v>
@@ -1390,28 +1347,28 @@
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.7">
       <c r="B3" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.75">
       <c r="B4" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.7">
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.75">
       <c r="B6" s="14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/作業票.xlsx
+++ b/作業票.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\Project-Chi2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sasaki Kengo\Project-Chi2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63385BF2-2FE6-4A25-991F-AF3152747FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80890B0C-3EA4-45EA-8C84-38E4CA67FD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{41B48087-E4EE-4E9E-AF83-941FF13AEAD0}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="37">
   <si>
     <t>タスク</t>
     <phoneticPr fontId="1"/>
@@ -305,6 +305,16 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵キャラの移動</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イドウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1007,7 +1017,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>34</v>
@@ -1180,9 +1190,11 @@
       <c r="C14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E14" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F14" s="2"/>
     </row>
@@ -1190,10 +1202,14 @@
       <c r="B15" s="8">
         <v>13</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="3"/>
+      <c r="C15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E15" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2"/>
     </row>

--- a/作業票.xlsx
+++ b/作業票.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coop2\Project-Chi2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\Project-Chi2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD8D650-C74E-4A75-AE8E-E75212413C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63385BF2-2FE6-4A25-991F-AF3152747FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{41B48087-E4EE-4E9E-AF83-941FF13AEAD0}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="36">
   <si>
     <t>タスク</t>
     <phoneticPr fontId="1"/>
@@ -78,44 +78,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Stater Assetという外部アセットを使用。けんご君の操作確認をくめたが確認し、運用可能と判断。
-なおコードは全く分からない。</t>
-    <rPh sb="15" eb="17">
-      <t>ガイブ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>クン</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ウンヨウ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>カノウ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ハンダン</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>マッタ</t>
-    </rPh>
-    <rPh sb="60" eb="61">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>弱攻撃</t>
     <rPh sb="0" eb="3">
       <t>ジャクコウゲキ</t>
@@ -130,31 +92,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">ダメージ判定は未実装。範囲：半径1m, 角度-30~30度前方　 </t>
-    <rPh sb="4" eb="6">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>ミジッソウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ハンイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ハンケイ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>カクド</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ゼンポウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ダメージ計算</t>
     <rPh sb="4" eb="6">
       <t>ケイサン</t>
@@ -223,21 +160,151 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>運、相性倍率（表示問題）のデータ形式は要相談。</t>
+    <t>インベントリ作成</t>
+    <rPh sb="6" eb="8">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細は以下の通り</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>くめた</t>
+  </si>
+  <si>
+    <t>インベントリ１：アイテム入手</t>
+    <rPh sb="12" eb="14">
+      <t>ニュウシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インベントリ２：アイテム消費</t>
+    <rPh sb="12" eb="14">
+      <t>ショウヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インベントリ３：指定アイテム数確認</t>
+    <rPh sb="8" eb="10">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インベントリ４：所持アイテム表示</t>
+    <rPh sb="8" eb="10">
+      <t>ショジ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕様書はまだ。</t>
+    <rPh sb="0" eb="3">
+      <t>シヨウショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フロー作成中</t>
+    <rPh sb="3" eb="6">
+      <t>サクセイチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>岩渕君とざっくりと仕様を確認してから？</t>
+    <rPh sb="0" eb="3">
+      <t>イワブチクン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムインターフェース</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SP回復</t>
+    <rPh sb="2" eb="4">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラ切り替え</t>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stater Assetという外部アセットを使用。けんご君の操作確認をくめたが確認し、運用可能と判断。</t>
+    <rPh sb="15" eb="17">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>クン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ウンヨウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ハンダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>運は削除</t>
     <rPh sb="0" eb="1">
       <t>ウン</t>
     </rPh>
-    <rPh sb="2" eb="6">
-      <t>アイショウバイリツ</t>
-    </rPh>
-    <rPh sb="7" eb="11">
-      <t>ヒョウジモンダイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ケイシキ</t>
-    </rPh>
-    <rPh sb="19" eb="22">
-      <t>ヨウソウダン</t>
+    <rPh sb="2" eb="4">
+      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -246,7 +313,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,12 +329,6 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -487,7 +548,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -516,9 +577,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
@@ -928,8 +986,8 @@
       <c r="C2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>22</v>
+      <c r="D2" s="15" t="s">
+        <v>20</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>1</v>
@@ -938,7 +996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="52.9" x14ac:dyDescent="0.7">
+    <row r="3" spans="2:6" ht="35.25" x14ac:dyDescent="0.7">
       <c r="B3" s="8">
         <v>1</v>
       </c>
@@ -946,13 +1004,13 @@
         <v>5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.7">
@@ -960,30 +1018,28 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B5" s="8">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -992,81 +1048,115 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B7" s="8">
         <v>5</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3"/>
+      <c r="C7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B8" s="8">
         <v>6</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="3"/>
+      <c r="C8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B9" s="8">
         <v>7</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="3"/>
+      <c r="C9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B10" s="8">
         <v>8</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="3"/>
+      <c r="C10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B11" s="8">
         <v>9</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="3"/>
+      <c r="C11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B12" s="8">
         <v>10</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="3"/>
+      <c r="C12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E12" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -1074,7 +1164,9 @@
       <c r="B13" s="8">
         <v>11</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="D13" s="3"/>
       <c r="E13" s="1" t="s">
         <v>3</v>
@@ -1085,7 +1177,9 @@
       <c r="B14" s="8">
         <v>12</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="D14" s="3"/>
       <c r="E14" s="1" t="s">
         <v>3</v>
@@ -1237,44 +1331,44 @@
   <sheetData>
     <row r="1" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.75">
       <c r="B1" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.7">
       <c r="B2" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.7">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="B4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="B4" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>12</v>
+      <c r="C4" s="11" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.7">
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="B6" s="15" t="s">
-        <v>21</v>
+      <c r="B6" s="14" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/作業票.xlsx
+++ b/作業票.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coop2\Project-Chi2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sasaki Kengo\Project-Chi2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD8D650-C74E-4A75-AE8E-E75212413C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B78A639-F959-4C66-B926-B67CA37A4E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{41B48087-E4EE-4E9E-AF83-941FF13AEAD0}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="25">
   <si>
     <t>タスク</t>
     <phoneticPr fontId="1"/>
@@ -238,6 +238,16 @@
     </rPh>
     <rPh sb="19" eb="22">
       <t>ヨウソウダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1008,10 +1018,14 @@
       <c r="B7" s="8">
         <v>5</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3"/>
+      <c r="C7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F7" s="10"/>
     </row>

--- a/作業票.xlsx
+++ b/作業票.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\Project-Chi2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63385BF2-2FE6-4A25-991F-AF3152747FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A750A159-BB43-42E8-8177-63CCB3D1496A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{41B48087-E4EE-4E9E-AF83-941FF13AEAD0}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
   <si>
     <t>タスク</t>
     <phoneticPr fontId="1"/>
@@ -305,6 +305,96 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵キャラの移動</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武器</t>
+    <rPh sb="0" eb="2">
+      <t>ブキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武器１：武器のステータス、サブ効果</t>
+    <rPh sb="0" eb="2">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武器２：武器のサブ効果追加</t>
+    <rPh sb="0" eb="2">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>コウカツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武器３：プレイヤーへ武器の実ステータスの合算処理</t>
+    <rPh sb="0" eb="2">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ジツ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ガッサン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーのステータスを受け取り、武器の効果を含めたステータスを合算して返す処理。</t>
+    <rPh sb="12" eb="13">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ガッサン</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ショリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1007,7 +1097,7 @@
         <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>34</v>
@@ -1167,7 +1257,9 @@
       <c r="C13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E13" s="1" t="s">
         <v>3</v>
       </c>
@@ -1180,9 +1272,11 @@
       <c r="C14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E14" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F14" s="2"/>
     </row>
@@ -1190,10 +1284,14 @@
       <c r="B15" s="8">
         <v>13</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="3"/>
+      <c r="C15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E15" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -1201,10 +1299,14 @@
       <c r="B16" s="8">
         <v>14</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="3"/>
+      <c r="C16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E16" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F16" s="2"/>
     </row>
@@ -1212,10 +1314,14 @@
       <c r="B17" s="8">
         <v>15</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="3"/>
+      <c r="C17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E17" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -1223,21 +1329,31 @@
       <c r="B18" s="8">
         <v>16</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="3"/>
+      <c r="C18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B19" s="8">
         <v>17</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="3"/>
+      <c r="C19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E19" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F19" s="2"/>
     </row>

--- a/作業票.xlsx
+++ b/作業票.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\Project-Chi2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A750A159-BB43-42E8-8177-63CCB3D1496A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7167309-848D-40A1-BDD3-637F94398928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{41B48087-E4EE-4E9E-AF83-941FF13AEAD0}"/>
   </bookViews>
@@ -326,19 +326,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>武器１：武器のステータス、サブ効果</t>
-    <rPh sb="0" eb="2">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>コウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>武器２：武器のサブ効果追加</t>
     <rPh sb="0" eb="2">
       <t>ブキ</t>
@@ -395,6 +382,22 @@
     </rPh>
     <rPh sb="38" eb="40">
       <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武器１：武器のステータス、サブ効果のデータ実装</t>
+    <rPh sb="0" eb="2">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1315,13 +1318,13 @@
         <v>15</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -1330,16 +1333,13 @@
         <v>16</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.7">
@@ -1347,7 +1347,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>23</v>
@@ -1355,7 +1355,9 @@
       <c r="E19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F19" s="2"/>
+      <c r="F19" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B20" s="8">

--- a/作業票.xlsx
+++ b/作業票.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\Project-Chi2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7167309-848D-40A1-BDD3-637F94398928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DCAF8C-33E8-4244-94C8-6508D832B7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{41B48087-E4EE-4E9E-AF83-941FF13AEAD0}"/>
   </bookViews>
@@ -319,13 +319,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>武器</t>
-    <rPh sb="0" eb="2">
-      <t>ブキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>武器２：武器のサブ効果追加</t>
     <rPh sb="0" eb="2">
       <t>ブキ</t>
@@ -339,53 +332,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>武器３：プレイヤーへ武器の実ステータスの合算処理</t>
-    <rPh sb="0" eb="2">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ジツ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ガッサン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ショリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤーのステータスを受け取り、武器の効果を含めたステータスを合算して返す処理。</t>
-    <rPh sb="12" eb="13">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ガッサン</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>カエ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ショリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>武器１：武器のステータス、サブ効果のデータ実装</t>
     <rPh sb="0" eb="2">
       <t>ブキ</t>
@@ -398,6 +344,51 @@
     </rPh>
     <rPh sb="21" eb="23">
       <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武器３：武器の総ステータス取得</t>
+    <rPh sb="4" eb="6">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シュトクブキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武器の基礎ステータスに効果を適用して返す。※5/21 仕様変更しました。</t>
+    <rPh sb="0" eb="2">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>テキヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="27" eb="31">
+      <t>シヨウヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武器（基本構造）</t>
+    <rPh sb="0" eb="2">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>キホンコウゾウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1303,13 +1294,13 @@
         <v>14</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" s="2"/>
     </row>
@@ -1318,7 +1309,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>23</v>
@@ -1333,7 +1324,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>23</v>
@@ -1353,7 +1344,7 @@
         <v>23</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>40</v>

--- a/作業票.xlsx
+++ b/作業票.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coop2\Project-Chi2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A750A159-BB43-42E8-8177-63CCB3D1496A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00268059-F2C9-42FB-86C9-E82E3E25343B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{41B48087-E4EE-4E9E-AF83-941FF13AEAD0}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="43">
   <si>
     <t>タスク</t>
     <phoneticPr fontId="1"/>
@@ -394,6 +394,19 @@
       <t>カエ</t>
     </rPh>
     <rPh sb="38" eb="40">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>店基本処理</t>
+    <rPh sb="0" eb="1">
+      <t>ミセ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
       <t>ショリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1261,7 +1274,7 @@
         <v>16</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -1361,10 +1374,14 @@
       <c r="B20" s="8">
         <v>18</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="3"/>
+      <c r="C20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E20" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F20" s="2"/>
     </row>

--- a/作業票.xlsx
+++ b/作業票.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coop2\Project-Chi2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.d\Project-Chi2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00268059-F2C9-42FB-86C9-E82E3E25343B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78ED7EA5-8ED9-485D-BF53-231A84754159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{41B48087-E4EE-4E9E-AF83-941FF13AEAD0}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="54">
   <si>
     <t>タスク</t>
     <phoneticPr fontId="1"/>
@@ -319,86 +319,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>武器</t>
-    <rPh sb="0" eb="2">
-      <t>ブキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>武器１：武器のステータス、サブ効果</t>
-    <rPh sb="0" eb="2">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>コウカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>武器２：武器のサブ効果追加</t>
-    <rPh sb="0" eb="2">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="9" eb="13">
-      <t>コウカツイカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>武器３：プレイヤーへ武器の実ステータスの合算処理</t>
-    <rPh sb="0" eb="2">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ジツ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ガッサン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ショリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤーのステータスを受け取り、武器の効果を含めたステータスを合算して返す処理。</t>
-    <rPh sb="12" eb="13">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ガッサン</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>カエ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ショリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>店基本処理</t>
     <rPh sb="0" eb="1">
       <t>ミセ</t>
@@ -408,6 +328,85 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武器（基本構造）</t>
+  </si>
+  <si>
+    <t>作業完了</t>
+  </si>
+  <si>
+    <t>武器１：武器のステータス、サブ効果のデータ実装</t>
+  </si>
+  <si>
+    <t>武器２：武器のサブ効果追加</t>
+  </si>
+  <si>
+    <t>武器３：武器の総ステータス取得</t>
+  </si>
+  <si>
+    <t>武器の基礎ステータスに効果を適用して返す。※5/21 仕様変更しました。</t>
+  </si>
+  <si>
+    <t>メニュー</t>
+  </si>
+  <si>
+    <t>未達成</t>
+  </si>
+  <si>
+    <t>インベントリやクエスト進捗などを開く。</t>
+  </si>
+  <si>
+    <t>シナリオ管理</t>
+  </si>
+  <si>
+    <t>ScenarioManagerクラスを作る。</t>
+  </si>
+  <si>
+    <t>シナリオ管理1：</t>
+  </si>
+  <si>
+    <t>プレイヤーの総ステータス確認</t>
+    <rPh sb="6" eb="7">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>くめた</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーデータを受け取り、装備やバフを返す。※実装後にバフに適応させる</t>
+    <rPh sb="9" eb="10">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ソウビ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>ジッソウゴ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>テキオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バフ実装</t>
+    <rPh sb="2" eb="4">
+      <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -708,13 +707,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
@@ -730,6 +722,13 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1070,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41F50AC-64FE-4975-A154-19305FADBFE4}">
-  <dimension ref="B1:F23"/>
+  <dimension ref="B1:F27"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="1.8125" customWidth="1"/>
@@ -1313,13 +1312,13 @@
         <v>14</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F16" s="2"/>
     </row>
@@ -1328,13 +1327,13 @@
         <v>15</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -1343,39 +1342,39 @@
         <v>16</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>41</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="F18" s="2"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B19" s="8">
         <v>17</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B20" s="8">
         <v>18</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>16</v>
@@ -1389,46 +1388,108 @@
       <c r="B21" s="8">
         <v>19</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="D21" s="3"/>
       <c r="E21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B22" s="8">
         <v>20</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="D22" s="3"/>
       <c r="E22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.7">
       <c r="B23" s="8">
         <v>21</v>
       </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="D23" s="3"/>
       <c r="E23" s="1" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.7">
+      <c r="B24" s="8">
+        <v>22</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.7">
+      <c r="B25" s="8">
+        <v>23</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.7">
+      <c r="B26" s="8">
+        <v>24</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.7">
+      <c r="B27" s="8">
+        <v>25</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="B2:F23" xr:uid="{B41F50AC-64FE-4975-A154-19305FADBFE4}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="作業完了">
+  <conditionalFormatting sqref="E29:E1048576 E1:E27">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="作業完了">
       <formula>NOT(ISERROR(SEARCH("作業完了",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="作業中">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="作業中">
       <formula>NOT(ISERROR(SEARCH("作業中",E1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="未達成">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="未達成">
       <formula>NOT(ISERROR(SEARCH("未達成",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1440,13 +1501,13 @@
           <x14:formula1>
             <xm:f>Sheet2!$C$2:$C$4</xm:f>
           </x14:formula1>
-          <xm:sqref>E1:E1048576</xm:sqref>
+          <xm:sqref>E29:E1048576 E1:E27</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C37E05EE-FB64-46F8-B962-042D2DB124A7}">
           <x14:formula1>
             <xm:f>Sheet2!$B$2:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D1048576</xm:sqref>
+          <xm:sqref>D29:D1048576 D3:D23</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1507,7 +1568,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="D1">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="未達成">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="未達成">
       <formula>NOT(ISERROR(SEARCH("未達成",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
